--- a/survey_templates/024_discover_your_character_personality--survey_templates.xlsx
+++ b/survey_templates/024_discover_your_character_personality--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C112"/>
+  <dimension ref="A1:C90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>istj</t>
+          <t>estp</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ISTJ</t>
+          <t>ESTP</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>estp</t>
+          <t>estj</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ESTP</t>
+          <t>ESTJ</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>estj</t>
+          <t>estf</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ESTJ</t>
+          <t>ESTF</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>estf</t>
+          <t>intj</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ESTF</t>
+          <t>INTJ</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>entp</t>
+          <t>istf</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ENTP</t>
+          <t>ISTF</t>
         </is>
       </c>
     </row>
@@ -1505,1506 +1505,1132 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>enfp</t>
+          <t>isfp</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ENFP</t>
+          <t>ISFP</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>personality_type_choices</t>
+          <t>preferences_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>enf</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ENF</t>
+          <t>Morning</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>personality_type_choices</t>
+          <t>preferences_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>intp</t>
+          <t>evening</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>INTP</t>
+          <t>Evening</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>personality_type_choices</t>
+          <t>preferences_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>intp</t>
+          <t>afternoon</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>INTP</t>
+          <t>Afternoon</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>personality_type_choices</t>
+          <t>preferences_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>intj</t>
+          <t>night</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>INTJ</t>
+          <t>Night</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>personality_type_choices</t>
+          <t>preferences_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>intp</t>
+          <t>weekdays</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>INTP</t>
+          <t>Weekdays</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>personality_type_choices</t>
+          <t>preferences_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>istf</t>
+          <t>weekend</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ISTF</t>
+          <t>Weekend</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>personality_type_choices</t>
+          <t>communication_style_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>isfp</t>
+          <t>verbal</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ISFP</t>
+          <t>Verbal</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>personality_type_choices</t>
+          <t>communication_style_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>esfp</t>
+          <t>non-verbal</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ESFP</t>
+          <t>Non-verbal</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>personality_type_choices</t>
+          <t>communication_style_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>esfp</t>
+          <t>body_language</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ESFP</t>
+          <t>Body language</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>personality_type_choices</t>
+          <t>conflict_style_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>esfj</t>
+          <t>competitive</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ESFJ</t>
+          <t>Competitive</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>personality_type_choices</t>
+          <t>conflict_style_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>enf</t>
+          <t>collaborative</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ENF</t>
+          <t>Collaborative</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>personality_type_choices</t>
+          <t>conflict_style_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>estf</t>
+          <t>avoidant</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ESTF</t>
+          <t>Avoidant</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>personality_type_choices</t>
+          <t>conflict_style_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>esfp</t>
+          <t>accommodative</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ESFP</t>
+          <t>Accommodative</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>personality_type_choices</t>
+          <t>decision_making_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>esfp</t>
+          <t>rational</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ESFP</t>
+          <t>Rational</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>personality_type_choices</t>
+          <t>decision_making_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>intp</t>
+          <t>emotional</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>INTP</t>
+          <t>Emotional</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>personality_type_choices</t>
+          <t>decision_making_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>estj</t>
+          <t>intuitive</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ESTJ</t>
+          <t>Intuitive</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>personality_type_choices</t>
+          <t>decision_making_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>enfp</t>
+          <t>impulsive</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ENFP</t>
+          <t>Impulsive</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>personality_type_choices</t>
+          <t>decision_making_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>estp</t>
+          <t>spontaneous</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ESTP</t>
+          <t>Spontaneous</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>personality_type_choices</t>
+          <t>work_style_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>estj</t>
+          <t>autonomy</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ESTJ</t>
+          <t>Autonomy</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>personality_type_choices</t>
+          <t>work_style_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>esfp</t>
+          <t>structure</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ESFP</t>
+          <t>Structure</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>personality_type_choices</t>
+          <t>work_style_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>estj</t>
+          <t>flexibility</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ESTJ</t>
+          <t>Flexibility</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>preferences_choices</t>
+          <t>work_style_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>morning</t>
+          <t>creativity</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Creativity</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>preferences_choices</t>
+          <t>work_style_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>evening</t>
+          <t>independence</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Independence</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>preferences_choices</t>
+          <t>work_style_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>afternoon</t>
+          <t>teamwork</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Afternoon</t>
+          <t>Teamwork</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>preferences_choices</t>
+          <t>values_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>night</t>
+          <t>honesty</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Night</t>
+          <t>Honesty</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>preferences_choices</t>
+          <t>values_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>weekdays</t>
+          <t>authenticity</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Weekdays</t>
+          <t>Authenticity</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>preferences_choices</t>
+          <t>values_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>weekend</t>
+          <t>empathy</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Weekend</t>
+          <t>Empathy</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>communication_style_choices</t>
+          <t>values_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>verbal</t>
+          <t>fairness</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Verbal</t>
+          <t>Fairness</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>communication_style_choices</t>
+          <t>values_choices</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>non-verbal</t>
+          <t>justice</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Non-verbal</t>
+          <t>Justice</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>communication_style_choices</t>
+          <t>values_choices</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>body_language</t>
+          <t>autonomy</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Body language</t>
+          <t>Autonomy</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>conflict_style_choices</t>
+          <t>goals_choices</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>competitive</t>
+          <t>short-term</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Competitive</t>
+          <t>Short-term</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>conflict_style_choices</t>
+          <t>goals_choices</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>collaborative</t>
+          <t>long-term</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Collaborative</t>
+          <t>Long-term</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>conflict_style_choices</t>
+          <t>self_care_choices</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>avoidant</t>
+          <t>essential</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avoidant</t>
+          <t>Essential</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>conflict_style_choices</t>
+          <t>self_care_choices</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>accommodative</t>
+          <t>important</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Accommodative</t>
+          <t>Important</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>decision_making_choices</t>
+          <t>self_care_choices</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>rational</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Rational</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>decision_making_choices</t>
+          <t>self_care_choices</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>emotional</t>
+          <t>not_important</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Emotional</t>
+          <t>Not Important</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>decision_making_choices</t>
+          <t>self_care_choices</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>intuitive</t>
+          <t>very_important</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Intuitive</t>
+          <t>Very important</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>decision_making_choices</t>
+          <t>stress_management_choices</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>impulsive</t>
+          <t>mindfulness</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Impulsive</t>
+          <t>Mindfulness</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>decision_making_choices</t>
+          <t>stress_management_choices</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>spontaneous</t>
+          <t>distraction</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spontaneous</t>
+          <t>Distraction</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>work_style_choices</t>
+          <t>stress_management_choices</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>autonomy</t>
+          <t>acceptance</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Autonomy</t>
+          <t>Acceptance</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>work_style_choices</t>
+          <t>relationships_choices</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>structure</t>
+          <t>single</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Structure</t>
+          <t>Single</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>work_style_choices</t>
+          <t>relationships_choices</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>flexibility</t>
+          <t>in_a_relationship</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Flexibility</t>
+          <t>In a relationship</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>work_style_choices</t>
+          <t>relationships_choices</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>creativity</t>
+          <t>married</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Creativity</t>
+          <t>Married</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>work_style_choices</t>
+          <t>relationships_choices</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>independence</t>
+          <t>widowed</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Independence</t>
+          <t>Widowed</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>work_style_choices</t>
+          <t>relationships_choices</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>teamwork</t>
+          <t>divorced</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Teamwork</t>
+          <t>Divorced</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>values_choices</t>
+          <t>education_choices</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>honesty</t>
+          <t>high_school</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Honesty</t>
+          <t>High school</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>values_choices</t>
+          <t>education_choices</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>authenticity</t>
+          <t>college</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Authenticity</t>
+          <t>College</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>values_choices</t>
+          <t>education_choices</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>empathy</t>
+          <t>university</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Empathy</t>
+          <t>University</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>values_choices</t>
+          <t>education_choices</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>fairness</t>
+          <t>bachelor's</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Fairness</t>
+          <t>Bachelor's</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>values_choices</t>
+          <t>education_choices</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>justice</t>
+          <t>master's</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Justice</t>
+          <t>Master's</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>values_choices</t>
+          <t>education_choices</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>autonomy</t>
+          <t>ph.d.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Autonomy</t>
+          <t>Ph.D.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>goals_choices</t>
+          <t>work_history_choices</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>short-term</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Short-term</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>goals_choices</t>
+          <t>work_history_choices</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>long-term</t>
+          <t>part-time</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Long-term</t>
+          <t>Part-time</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>self_care_choices</t>
+          <t>work_history_choices</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>essential</t>
+          <t>full-time</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Essential</t>
+          <t>Full-time</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>self_care_choices</t>
+          <t>work_history_choices</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>important</t>
+          <t>multiple</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Important</t>
+          <t>Multiple</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>self_care_choices</t>
+          <t>personality_assessment_choices</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>self_care_choices</t>
+          <t>personality_assessment_choices</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>not_important</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Not Important</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>self_care_choices</t>
+          <t>personality_assessment_choices</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>very_important</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Very important</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>stress_management_choices</t>
+          <t>personality_score_choices</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>mindfulness</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Mindfulness</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>stress_management_choices</t>
+          <t>personality_score_choices</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>mindfulness</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Mindfulness</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>stress_management_choices</t>
+          <t>personality_score_choices</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>distraction</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Distraction</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>stress_management_choices</t>
+          <t>personality_type_score_choices</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>acceptance</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Acceptance</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>relationships_choices</t>
+          <t>personality_type_score_choices</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>single</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Single</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>relationships_choices</t>
+          <t>personality_type_score_choices</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>in_a_relationship</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>In a relationship</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>relationships_choices</t>
+          <t>final_question_choices</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>married</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Married</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>relationships_choices</t>
+          <t>final_question_choices</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>widowed</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
-        <is>
-          <t>Widowed</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>relationships_choices</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>divorced</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Divorced</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>education_choices</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>high_school</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>High school</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>education_choices</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>college</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>College</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>education_choices</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>university</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>University</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>education_choices</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>bachelor's</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Bachelor's</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>education_choices</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>master's</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Master's</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>education_choices</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>ph.d.</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Ph.D.</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>work_history_choices</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>work_history_choices</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>part-time</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Part-time</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>work_history_choices</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>full-time</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Full-time</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>work_history_choices</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>multiple</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Multiple</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>personality_assessment_choices</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>personality_assessment_choices</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>personality_assessment_choices</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>personality_score_choices</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>personality_score_choices</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>personality_score_choices</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>personality_type_score_choices</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>personality_type_score_choices</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>personality_type_score_choices</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>final_question_choices</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>final_question_choices</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
         <is>
           <t>False</t>
         </is>
